--- a/Documentación/Modulo 1/Matriz de trazabilidad.xlsx
+++ b/Documentación/Modulo 1/Matriz de trazabilidad.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07bf06ea44ecd913/UAM/TRIMESTRE 26-I/INGENIERIA DE SOFTWARE/Modulo 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF9D30F0-41CC-4CFF-B287-07BEF2913399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{EF9D30F0-41CC-4CFF-B287-07BEF2913399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{254F47C4-FDC7-414D-BC82-914F40938763}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E68FD1D2-0B37-4C00-8139-9C36BC7552F4}"/>
   </bookViews>
@@ -56,9 +56,6 @@
     <t>RF-01</t>
   </si>
   <si>
-    <t xml:space="preserve">Registro de aspirantes con validación de identidad (CURP/RFC). </t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Clase </t>
     </r>
@@ -221,6 +218,9 @@
   </si>
   <si>
     <t xml:space="preserve">Log inmutable de cambios en tablas. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registro de aspirantes con validación de identidad (CURP). </t>
   </si>
 </sst>
 </file>
@@ -812,84 +812,84 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="7" t="s">
         <v>8</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="80.25" customHeight="1">
       <c r="B4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="7" t="s">
         <v>13</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="57">
       <c r="B5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="70.5" customHeight="1">
       <c r="B6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>22</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="88.5" customHeight="1" thickBot="1">
       <c r="B7" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="F7" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="15.75" thickTop="1"/>
